--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/24 12:36:33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21428.57</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/24 12:08:55</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>24096.39</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>380000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45524.96</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>24096.39</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>45524.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>06/24 14:10:57</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>45524</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>380000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>45524.96</t>
+          <t>380000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45524.96</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>45524</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>45524.96</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/24 12:36:33</t>
+          <t>06/25 16:34:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>48192.77</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>06/24 12:08:55</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>24096.39</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>羊美云</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/24 14:10:57</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>45524</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>400000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>48192.77</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>380000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>45524.96</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>45524</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.96</t>
+          <t>48192.77</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06/25 19:22:04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>400000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>400000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48192.77</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>48192</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>48192.77</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.77</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/25 16:34:17</t>
+          <t>06/26 14:40:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>06/25 19:22:04</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>48192</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48192.77</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>48192</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.77</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06/26 16:07:20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/26 14:40:59</t>
+          <t>06/27 11:42:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>06/26 16:07:20</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11904</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.76</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/27 13:03:05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6172.84</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/27 11:42:49</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>350000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42317.42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>36144.58</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>42317.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>06/27 13:07:43</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>42317</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>350000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>42317.42</t>
+          <t>350000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42317.42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>42317</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>42317.42</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/27 13:03:05</t>
+          <t>06/29 12:46:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,237 +90,168 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>林伟超</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>06/27 11:42:49</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>36144.58</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/27 13:07:43</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>42317</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>24096.39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>42317.42</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>42317</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.42</t>
+          <t>24096.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06/29 14:04:21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>24096</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24096.39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>24096</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>24096.39</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/29 12:46:37</t>
+          <t>06/30 10:08:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>06/29 14:04:21</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>24096</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>500000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>60240.96</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24096</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.39</t>
+          <t>60240.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/30 10:22:52</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>114634.15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/30 10:08:02</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>60240.96</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>1440000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174875.11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>60240.96</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>174875.11</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06/30 10:22:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>114634.15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>06/30 10:08:02</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>60240.96</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1440000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>174875.11</t>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208610.05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>174875.11</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>208610.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -283,59 +283,86 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>06/30 11:35:36</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>79000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1720000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>208610.05</t>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208610.05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>79000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>208610.05</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>129610.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>06/30 11:50:16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>06/30 11:35:36</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>79000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1720000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>208610.05</t>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>208610.05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>129610.05</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>68610.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -313,83 +313,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>06/30 11:50:16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>06/30 11:35:36</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>79000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1720000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>208610.05</t>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>208610.05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>208610</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>68610.05</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,166 +159,181 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06/30 10:22:52</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>114634.15</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>06/30 10:08:02</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>60240.96</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -328,7 +343,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -340,83 +355,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>06/30 11:50:16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>06/30 11:35:36</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>79000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1720000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>208610.05</t>
+          <t>2040000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>208610</t>
+          <t>247164.27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>208610</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0.05</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>38554.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,166 +201,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06/30 10:22:52</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>114634.15</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>06/30 10:08:02</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>60240.96</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -370,7 +385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -382,83 +397,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>06/30 11:50:16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>06/30 11:35:36</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>79000</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2040000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>247164.27</t>
+          <t>2320000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>208610</t>
+          <t>280899.21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>208610</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>38554.27</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>72289.21</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -385,7 +385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -412,7 +412,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -424,83 +424,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>06/30 11:50:16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>06/30 11:35:36</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>79000</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2320000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>280899.21</t>
+          <t>2320000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>208610</t>
+          <t>280899.21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>280899</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>72289.21</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.21</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/01 15:40:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>250000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30120.48</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>林伟超</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/01 14:50:11</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>390000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>46987.95</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>向文</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>390000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>46987.95</t>
+          <t>640000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77108.43</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>46987.95</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>77108.43</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07/01 16:52:50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>77108</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>640000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>77108.43</t>
+          <t>640000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77108.43</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>77108</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>77108.43</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.43</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 15:40:01</t>
+          <t>07/01 18:40:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>林伟超</t>
+          <t>:安徽省阜阳市临泉县杨桥镇 安徽 明天 9.00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>nn40007</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/01 15:40:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>250000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30120.48</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>林伟超</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/01 14:50:11</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>390000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>46987.95</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>向文</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/01 16:52:50</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>77108</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>640000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>77108.43</t>
+          <t>639990</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>77098.43</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>77108</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.43</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>-9.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/02 12:32:59</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>27710</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>230000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27710.84</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>27710</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>27710.84</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/02 15:47:40</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1064400</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>128240.96</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>羊美云</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/02 09:17:34</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>230000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>27710.84</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>王志宽</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/02 12:32:59</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>27710</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>230000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>1294400</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>155951.81</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>27710</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.84</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>128241.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07/02 19:00:39</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>128241</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/02 12:32:59</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>27710</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1294400</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>155951.81</t>
+          <t>1294400</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>155951.81</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>155951</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>128241.81</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/02 15:47:40</t>
+          <t>07/03 20:29:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,264 +90,168 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>128240.96</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>moucai1111</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/02 09:17:34</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>230000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>27710.84</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>王志宽</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/02 19:00:39</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>128241</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/02 12:32:59</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27710</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1294400</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>155951.81</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>155951</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.81</t>
+          <t>-12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/03 20:29:29</t>
+          <t>07/04 15:50:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,27 +90,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t>向超</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>moucai1111</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>170000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>20238.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/04 17:10:11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20238</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>170000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>170000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20238.1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20238</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20238.1</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/04 15:50:29</t>
+          <t>07/06 16:38:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>向超</t>
+          <t>孔令智</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/04 17:10:11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>20238</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20238</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.1</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/06 17:52:23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/06 16:38:03</t>
+          <t>07/09 09:53:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -100,12 +100,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>孔令智</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/06 17:52:23</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11904</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.76</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/09 09:54:13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>370000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>44578.31</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>羊美云</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/09 09:53:40</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>11904.76</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>470000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56483.08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>56483.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -13,7 +13,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>群组：金鑫供大牛全国取现</t>
+          <t>群组：金鑫供大牛全国取现DD</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07/09 11:40:53</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>56483</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>470000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>56483.08</t>
+          <t>470000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56483.08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>56483</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>56483.08</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09 09:54:13</t>
+          <t>07/10 13:45:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t>向文</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/09 09:53:40</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>11904.76</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/09 11:40:53</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>56483</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>470000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>56483.08</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>56483</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.08</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/10 14:56:17</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/10 13:45:23</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>11904.76</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>向文</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>400000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48049.34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>48049.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07/10 18:27:46</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>48049</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>400000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48049.34</t>
+          <t>400000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48049.34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>48049</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>48049.34</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/10 14:56:17</t>
+          <t>07/12 18:24:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/10 13:45:23</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>11904.76</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>向文</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/10 18:27:46</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>48049</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7407.41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>48049.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>48049</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.34</t>
+          <t>7407.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/12 18:26:46</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>60000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>60000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7407.41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>7407.41</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6407.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>07/12 18:39:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6407</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/12 18:26:46</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>60000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>60000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7407.41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>6407.41</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/12 18:24:59</t>
+          <t>07/14 19:36:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/12 18:39:01</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6407</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/12 18:26:46</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>230000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>27710.84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7407.41</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>7407</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.41</t>
+          <t>27710.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/14 20:52:08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>27710</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>230000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27710.84</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>27710</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>27710.84</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/14 19:36:37</t>
+          <t>07/17 17:11:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/14 20:52:08</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>27710</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>250000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>30120.48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27710</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.84</t>
+          <t>30120.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/17 18:15:22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>183843</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21886.07</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/17 17:11:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>250000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>30120.48</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>250000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>433843</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52006.55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>30120.48</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>52006.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07/17 19:45:53</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>52006</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>433843</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>52006.55</t>
+          <t>433843</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52006.55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>52006</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>52006.55</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 18:15:22</t>
+          <t>07/18 15:08:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,237 +90,168 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21886.07</t>
+          <t>10790.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>马瑞昭</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/17 17:11:15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>250000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>30120.48</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>羊美云</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 19:45:53</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>52006</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>87400</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10790.12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>433843</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>52006.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>52006</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.55</t>
+          <t>10790.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/18 17:18:15</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10790</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>87400</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10790.12</t>
+          <t>87400</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10790.12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10790</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10790.12</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/18 15:08:49</t>
+          <t>07/21 19:05:10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10790.12</t>
+          <t>434.78</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>马瑞昭</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/18 17:18:15</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>10790</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>434.78</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10790.12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10790</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.12</t>
+          <t>434.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/21 20:19:37</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>5000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>434.78</t>
+          <t>5000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>434.78</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>434.78</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/21 19:05:10</t>
+          <t>07/22 14:50:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>434.78</t>
+          <t>27380.95</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/21 20:19:37</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>230000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>27380.95</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>434.78</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>434</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.78</t>
+          <t>27380.95</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/22 14:51:36</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>44950</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5351.19</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>耿振云</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/22 14:50:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>230000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>27380.95</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>耿振云</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>230000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27380.95</t>
+          <t>274950</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32732.14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>27380.95</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>32732.14</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07/22 16:14:19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>32732</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>274950</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32732.14</t>
+          <t>274950</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32732.14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>32732</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>32732.14</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.14</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22 14:51:36</t>
+          <t>07/23 09:59:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44950</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5351.19</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>羊美云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/22 14:50:15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>230000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>27380.95</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>耿振云</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/22 16:14:19</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>32732</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>420000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32732.14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>32732</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.14</t>
+          <t>50000</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/23 12:09:30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>420000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>420000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>50000</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/23 09:59:06</t>
+          <t>07/25 14:41:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>羊美云</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/23 12:09:30</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>50000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/25 19:35:03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>95990</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11033.33</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/25 14:41:17</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>11764.71</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>195990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22798.04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11764.71</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22798.04</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07/25 19:36:27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>22798</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>195990</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22798.04</t>
+          <t>195990</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22798.04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22798</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>22798.04</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.04</t>
         </is>
       </c>
     </row>
